--- a/output/pdf_financials_xlsx/WGT.xlsx
+++ b/output/pdf_financials_xlsx/WGT.xlsx
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.021795</v>
+        <v>1.203799</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>1.168898</v>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>2.648784</v>
+        <v>1.46678</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>-0.026332</v>
@@ -885,13 +885,13 @@
         <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.164235</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.180534</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.294976</v>
       </c>
     </row>
     <row r="13">
@@ -1581,13 +1581,13 @@
         <v>-0.29199</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-1.722128</v>
+        <v>-1.557893</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-3.039998</v>
+        <v>-2.859464</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-9.365963000000001</v>
+        <v>-9.070987000000001</v>
       </c>
     </row>
     <row r="28">
@@ -1665,13 +1665,13 @@
         <v>-0.29199</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-1.422236</v>
+        <v>-1.258001</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-1.904568</v>
+        <v>-1.724034</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-7.047323</v>
+        <v>-6.752347</v>
       </c>
     </row>
     <row r="30">
@@ -1709,7 +1709,7 @@
         <v>-1277.911505974003</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-571.1217749221966</v>
+        <v>-505.1705652042967</v>
       </c>
       <c r="K30" s="1" t="inlineStr">
         <is>
@@ -1834,31 +1834,31 @@
         <v>0</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.069364</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.316995</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>2.196213</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>2.767824</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.007412</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.026354</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>3.675427</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.743536</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>1.786474</v>
       </c>
     </row>
     <row r="35">
@@ -1914,31 +1914,31 @@
         <v>3.322543</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>1.159752</v>
+        <v>1.229116</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.316995</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>2.196213</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>2.767824</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.007412</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.026354</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>3.675427</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.743536</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>1.786474</v>
       </c>
     </row>
     <row r="37">
@@ -2394,31 +2394,31 @@
         <v>0.6944900000000001</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.560122</v>
+        <v>0.490758</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.370006</v>
+        <v>0.053011</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>3.272101</v>
+        <v>1.075888</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>2.888729</v>
+        <v>0.120905</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.117412</v>
+        <v>0.11</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.026354</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>3.726537</v>
+        <v>0.05111</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.047335</v>
+        <v>0.303799</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>2.409959</v>
+        <v>0.623485</v>
       </c>
     </row>
     <row r="49">
@@ -6138,7 +6138,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -14055,7 +14055,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -34962,7 +34962,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
@@ -47151,7 +47151,7 @@
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E584" s="5" t="n">

--- a/output/pdf_financials_xlsx/WGT.xlsx
+++ b/output/pdf_financials_xlsx/WGT.xlsx
@@ -4483,16 +4483,16 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.044964</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.044964</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.038591</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.014608</v>
       </c>
       <c r="F100" s="3" t="n">
         <v>0</v>
@@ -26996,7 +26996,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -29089,7 +29089,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -31568,7 +31568,7 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
@@ -32637,7 +32637,7 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E378" s="5" t="n">
@@ -45250,7 +45250,7 @@
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E557" t="inlineStr">
@@ -46520,7 +46520,11 @@
           <t>Amortization of intangible assets 8 &amp; 11</t>
         </is>
       </c>
-      <c r="D575" t="inlineStr"/>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E575" t="inlineStr">
         <is>
           <t>-</t>
@@ -47007,7 +47011,7 @@
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E582" s="5" t="n">

--- a/output/pdf_financials_xlsx/WGT.xlsx
+++ b/output/pdf_financials_xlsx/WGT.xlsx
@@ -657,19 +657,19 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.021795</v>
+        <v>0.055523</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.030661</v>
+        <v>0.06490899999999999</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.038316</v>
+        <v>0.07849100000000001</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.030337</v>
+        <v>0.073463</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0</v>
+        <v>0.031151</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>0</v>
@@ -789,7 +789,7 @@
         <v>0.77504</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>0.031151</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>0</v>
@@ -3182,10 +3182,10 @@
         <v>0</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.070102</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.059067</v>
       </c>
       <c r="H67" s="3" t="n">
         <v>0</v>
@@ -4741,10 +4741,10 @@
         <v>0.167991</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0</v>
+        <v>0.279794</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0</v>
+        <v>0.154149</v>
       </c>
       <c r="J106" s="3" t="n">
         <v>-0.113909</v>
@@ -4904,16 +4904,16 @@
         <v>0</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>0.005252</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>0</v>
+        <v>0.009303000000000001</v>
       </c>
       <c r="K110" s="3" t="n">
-        <v>0</v>
+        <v>0.093316</v>
       </c>
       <c r="L110" s="3" t="n">
-        <v>0</v>
+        <v>0.441221</v>
       </c>
     </row>
     <row r="111">
@@ -4929,7 +4929,7 @@
         <v>0</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001367</v>
       </c>
       <c r="E111" s="3" t="n">
         <v>0</v>
@@ -5885,7 +5885,7 @@
         <v>0</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001367</v>
       </c>
       <c r="E134" s="3" t="n">
         <v>0</v>
@@ -5925,7 +5925,7 @@
         <v>0.014958</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>0.34716</v>
+        <v>0.345793</v>
       </c>
       <c r="E135" s="3" t="n">
         <v>0.614802</v>
@@ -19064,7 +19064,11 @@
           <t>Accretion 15</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E187" t="inlineStr">
         <is>
           <t>-</t>
@@ -22673,7 +22677,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr"/>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr">
         <is>
           <t>-</t>
@@ -23022,7 +23030,11 @@
           <t>Accretion 7</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr">
         <is>
           <t>-</t>
@@ -23089,7 +23101,11 @@
           <t>Change in non-cash operating working capital 14</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr"/>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E244" t="inlineStr">
         <is>
           <t>-</t>
@@ -24006,7 +24022,11 @@
           <t>Change in non-cash operating working capital 13</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr"/>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E257" t="inlineStr">
         <is>
           <t>-</t>
@@ -24499,7 +24519,11 @@
           <t>Accretion 8</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr"/>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E264" t="inlineStr">
         <is>
           <t>-</t>
@@ -28008,7 +28032,11 @@
           <t>Disposition (purchase) of equipment 5 1,698</t>
         </is>
       </c>
-      <c r="D313" t="inlineStr"/>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E313" t="inlineStr">
         <is>
           <t>-</t>
@@ -30714,7 +30742,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D351" t="inlineStr"/>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E351" t="inlineStr">
         <is>
           <t>-</t>
@@ -41584,7 +41616,11 @@
           <t>Directors’ fees</t>
         </is>
       </c>
-      <c r="D505" t="inlineStr"/>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E505" t="inlineStr">
         <is>
           <t>-</t>
@@ -43558,7 +43594,11 @@
           <t>Directors' fees 31,151</t>
         </is>
       </c>
-      <c r="D533" t="inlineStr"/>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E533" t="inlineStr">
         <is>
           <t>-</t>
@@ -46104,7 +46144,11 @@
           <t>Net earnings (loss) $</t>
         </is>
       </c>
-      <c r="D569" t="inlineStr"/>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E569" t="inlineStr">
         <is>
           <t>-</t>
@@ -46593,7 +46637,11 @@
           <t>Directors' fees</t>
         </is>
       </c>
-      <c r="D576" t="inlineStr"/>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E576" s="5" t="n">
         <v>0.033728</v>
       </c>
